--- a/Data/Raw_burials/no_c14_raw_burials.xlsx
+++ b/Data/Raw_burials/no_c14_raw_burials.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="650">
   <si>
     <t>ID</t>
   </si>
@@ -212,7 +212,7 @@
     <t>BBR-1</t>
   </si>
   <si>
-    <t>Gibaja et al., 2018; Oliva, 2014</t>
+    <t>Gibaja et al., 2018; Oliva, 2015</t>
   </si>
   <si>
     <t>BBR-2</t>
@@ -314,7 +314,7 @@
     <t>E28</t>
   </si>
   <si>
-    <t>Gibaja et al., 2017</t>
+    <t>Gibaja et al., 2017b</t>
   </si>
   <si>
     <t>Bòbila Madurell-Can Feu B</t>
@@ -413,7 +413,7 @@
     <t>UF1</t>
   </si>
   <si>
-    <t>Duboscq, 2017; Gibaja et al., 2017</t>
+    <t>Duboscq, 2017; Gibaja et al., 2017a</t>
   </si>
   <si>
     <t>UF5</t>
@@ -503,7 +503,7 @@
     <t>11--2</t>
   </si>
   <si>
-    <t>Gibaja et al., 2017; Placencia, 2016</t>
+    <t>Gibaja et al., 2017b; Placencia, 2016</t>
   </si>
   <si>
     <t>G-7</t>
@@ -620,7 +620,7 @@
     <t>SF-502</t>
   </si>
   <si>
-    <t>Gibaja and Martinez, 2015</t>
+    <t>Subirà et al., 2015</t>
   </si>
   <si>
     <t>Ca N'Agut</t>
@@ -773,6 +773,9 @@
     <t>EF3</t>
   </si>
   <si>
+    <t>Duboscq, 2017; Gibaja et al., 2017b</t>
+  </si>
+  <si>
     <t>Can Jorba</t>
   </si>
   <si>
@@ -899,7 +902,7 @@
     <t>SPC1</t>
   </si>
   <si>
-    <t>Duboscq, 2017; Monforte-Barberán, 2024</t>
+    <t>Duboscq, 2017; Monforte-Barberán, 2025</t>
   </si>
   <si>
     <t>SPC2</t>
@@ -1031,13 +1034,13 @@
     <t>CO-3</t>
   </si>
   <si>
-    <t>Comellatr del Mas de Baix</t>
+    <t>Comellar del Mas de Baix</t>
   </si>
   <si>
     <t>CMB</t>
   </si>
   <si>
-    <t>Miró, 1995</t>
+    <t>Miró et al., 1995</t>
   </si>
   <si>
     <t>Corbera</t>
@@ -1058,7 +1061,7 @@
     <t>Cova Mariver</t>
   </si>
   <si>
-    <t>Tarrus, 1978</t>
+    <t>Tarrus, 1979</t>
   </si>
   <si>
     <t>Cova Pasteral</t>
@@ -1067,7 +1070,7 @@
     <t>E-II</t>
   </si>
   <si>
-    <t>Campillo, Vives, 1986</t>
+    <t>Rosillo et al., 2025</t>
   </si>
   <si>
     <t>El Cementiri</t>
@@ -1379,10 +1382,10 @@
     <t>La Fossa del General</t>
   </si>
   <si>
-    <t>La RMonforte-Barberán, 2024la</t>
-  </si>
-  <si>
-    <t>RMonforte-Barberán, 2024</t>
+    <t>La Rambla</t>
+  </si>
+  <si>
+    <t>R1</t>
   </si>
   <si>
     <t>La Roqueta I</t>
@@ -1484,7 +1487,7 @@
     <t>MA</t>
   </si>
   <si>
-    <t>Vilardell et al., 1987</t>
+    <t>Vilardell et al., 1989</t>
   </si>
   <si>
     <t>Mas de Seròs</t>
@@ -1685,7 +1688,7 @@
     <t>PS</t>
   </si>
   <si>
-    <t>Monforte-Barberán, 2024</t>
+    <t>Monforte-Barberán, 2025</t>
   </si>
   <si>
     <t>Pla del Coll</t>
@@ -1775,7 +1778,7 @@
     <t>UF-II (XVI)</t>
   </si>
   <si>
-    <t>Gonzalez and Harzbecher inedit</t>
+    <t>González et al., 2017</t>
   </si>
   <si>
     <t>Sant Andreu de la Barca</t>
@@ -15023,7 +15026,7 @@
         <v>0.0</v>
       </c>
       <c r="O170" s="7" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="P170" s="5"/>
       <c r="Q170" s="5"/>
@@ -15059,10 +15062,10 @@
         <v>170</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D171" s="4">
         <v>1.79823872</v>
@@ -15134,10 +15137,10 @@
         <v>171</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D172" s="4">
         <v>2.06801318</v>
@@ -15209,10 +15212,10 @@
         <v>172</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D173" s="4">
         <v>2.440559169581682</v>
@@ -15284,10 +15287,10 @@
         <v>173</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D174" s="4">
         <v>2.2117425695937296</v>
@@ -15359,10 +15362,10 @@
         <v>174</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D175" s="4">
         <v>1.3699402436130583</v>
@@ -15434,10 +15437,10 @@
         <v>175</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D176" s="4">
         <v>2.442410059069681</v>
@@ -15509,10 +15512,10 @@
         <v>176</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D177" s="4">
         <v>2.442410059069681</v>
@@ -15584,10 +15587,10 @@
         <v>177</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D178" s="4">
         <v>2.442410059069681</v>
@@ -15659,10 +15662,10 @@
         <v>178</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D179" s="4">
         <v>2.442410059069681</v>
@@ -15734,10 +15737,10 @@
         <v>179</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D180" s="4">
         <v>2.130499754696959</v>
@@ -15809,10 +15812,10 @@
         <v>180</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D181" s="4">
         <v>1.9129874510429457</v>
@@ -15848,7 +15851,7 @@
         <v>0.0</v>
       </c>
       <c r="O181" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P181" s="5"/>
       <c r="Q181" s="5"/>
@@ -15884,10 +15887,10 @@
         <v>181</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D182" s="4">
         <v>1.9129874510429457</v>
@@ -15923,7 +15926,7 @@
         <v>0.0</v>
       </c>
       <c r="O182" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P182" s="5"/>
       <c r="Q182" s="5"/>
@@ -15959,10 +15962,10 @@
         <v>182</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D183" s="4">
         <v>2.184195769385063</v>
@@ -15998,7 +16001,7 @@
         <v>0.0</v>
       </c>
       <c r="O183" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P183" s="5"/>
       <c r="Q183" s="5"/>
@@ -16034,10 +16037,10 @@
         <v>183</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D184" s="4">
         <v>2.184195769385063</v>
@@ -16073,7 +16076,7 @@
         <v>0.0</v>
       </c>
       <c r="O184" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P184" s="5"/>
       <c r="Q184" s="5"/>
@@ -16109,10 +16112,10 @@
         <v>184</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D185" s="4">
         <v>1.7917156294750638</v>
@@ -16184,10 +16187,10 @@
         <v>185</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D186" s="4">
         <v>1.7917156294750638</v>
@@ -16259,7 +16262,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C187" s="3" t="s">
         <v>218</v>
@@ -16298,7 +16301,7 @@
         <v>0.0</v>
       </c>
       <c r="O187" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P187" s="5"/>
       <c r="Q187" s="5"/>
@@ -16334,10 +16337,10 @@
         <v>187</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D188" s="4">
         <v>1.2978553168480975</v>
@@ -16409,10 +16412,10 @@
         <v>188</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D189" s="4">
         <v>2.141635726199988</v>
@@ -16484,10 +16487,10 @@
         <v>189</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D190" s="4">
         <v>1.8613869954098146</v>
@@ -16559,10 +16562,10 @@
         <v>190</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D191" s="4">
         <v>1.6772120685598104</v>
@@ -16634,10 +16637,10 @@
         <v>191</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D192" s="4">
         <v>0.5613517398005937</v>
@@ -16709,10 +16712,10 @@
         <v>192</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D193" s="4">
         <v>2.1696760510673805</v>
@@ -16748,7 +16751,7 @@
         <v>0.0</v>
       </c>
       <c r="O193" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P193" s="5"/>
       <c r="Q193" s="5"/>
@@ -16784,10 +16787,10 @@
         <v>193</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D194" s="4">
         <v>2.1696760510673805</v>
@@ -16823,7 +16826,7 @@
         <v>0.0</v>
       </c>
       <c r="O194" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P194" s="5"/>
       <c r="Q194" s="5"/>
@@ -16859,10 +16862,10 @@
         <v>194</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D195" s="4">
         <v>2.1696760510673805</v>
@@ -16898,7 +16901,7 @@
         <v>0.0</v>
       </c>
       <c r="O195" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P195" s="5"/>
       <c r="Q195" s="5"/>
@@ -16934,10 +16937,10 @@
         <v>195</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D196" s="4">
         <v>2.1696760510673805</v>
@@ -16973,7 +16976,7 @@
         <v>0.0</v>
       </c>
       <c r="O196" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P196" s="5"/>
       <c r="Q196" s="5"/>
@@ -17009,10 +17012,10 @@
         <v>196</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D197" s="4">
         <v>2.1696760510673805</v>
@@ -17048,7 +17051,7 @@
         <v>0.0</v>
       </c>
       <c r="O197" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P197" s="5"/>
       <c r="Q197" s="5"/>
@@ -17084,10 +17087,10 @@
         <v>197</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D198" s="4">
         <v>2.1696760510673805</v>
@@ -17123,7 +17126,7 @@
         <v>0.0</v>
       </c>
       <c r="O198" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P198" s="5"/>
       <c r="Q198" s="5"/>
@@ -17159,10 +17162,10 @@
         <v>198</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D199" s="4">
         <v>2.1696760510673805</v>
@@ -17198,7 +17201,7 @@
         <v>0.0</v>
       </c>
       <c r="O199" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P199" s="5"/>
       <c r="Q199" s="5"/>
@@ -17234,10 +17237,10 @@
         <v>199</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D200" s="4">
         <v>2.1696760510673805</v>
@@ -17273,7 +17276,7 @@
         <v>0.0</v>
       </c>
       <c r="O200" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P200" s="5"/>
       <c r="Q200" s="5"/>
@@ -17309,10 +17312,10 @@
         <v>200</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D201" s="4">
         <v>2.1696760510673805</v>
@@ -17348,7 +17351,7 @@
         <v>0.0</v>
       </c>
       <c r="O201" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P201" s="5"/>
       <c r="Q201" s="5"/>
@@ -17384,10 +17387,10 @@
         <v>201</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D202" s="4">
         <v>2.1696760510673805</v>
@@ -17423,7 +17426,7 @@
         <v>0.0</v>
       </c>
       <c r="O202" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P202" s="5"/>
       <c r="Q202" s="5"/>
@@ -17459,10 +17462,10 @@
         <v>202</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D203" s="4">
         <v>2.1696760510673805</v>
@@ -17498,7 +17501,7 @@
         <v>0.0</v>
       </c>
       <c r="O203" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P203" s="5"/>
       <c r="Q203" s="5"/>
@@ -17534,10 +17537,10 @@
         <v>203</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D204" s="4">
         <v>2.1696760510673805</v>
@@ -17573,7 +17576,7 @@
         <v>0.0</v>
       </c>
       <c r="O204" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P204" s="5"/>
       <c r="Q204" s="5"/>
@@ -17609,10 +17612,10 @@
         <v>204</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D205" s="4">
         <v>2.1696760510673805</v>
@@ -17648,7 +17651,7 @@
         <v>0.0</v>
       </c>
       <c r="O205" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P205" s="5"/>
       <c r="Q205" s="5"/>
@@ -17684,10 +17687,10 @@
         <v>205</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D206" s="4">
         <v>2.1696760510673805</v>
@@ -17723,7 +17726,7 @@
         <v>0.0</v>
       </c>
       <c r="O206" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P206" s="5"/>
       <c r="Q206" s="5"/>
@@ -17759,10 +17762,10 @@
         <v>206</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D207" s="4">
         <v>2.1696760510673805</v>
@@ -17798,7 +17801,7 @@
         <v>0.0</v>
       </c>
       <c r="O207" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P207" s="5"/>
       <c r="Q207" s="5"/>
@@ -17834,10 +17837,10 @@
         <v>207</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D208" s="4">
         <v>2.1696760510673805</v>
@@ -17873,7 +17876,7 @@
         <v>0.0</v>
       </c>
       <c r="O208" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P208" s="5"/>
       <c r="Q208" s="5"/>
@@ -17909,10 +17912,10 @@
         <v>208</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D209" s="4">
         <v>2.1696760510673805</v>
@@ -17948,7 +17951,7 @@
         <v>0.0</v>
       </c>
       <c r="O209" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P209" s="5"/>
       <c r="Q209" s="5"/>
@@ -17984,10 +17987,10 @@
         <v>209</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D210" s="4">
         <v>2.1696760510673805</v>
@@ -18023,7 +18026,7 @@
         <v>0.0</v>
       </c>
       <c r="O210" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P210" s="5"/>
       <c r="Q210" s="5"/>
@@ -18059,10 +18062,10 @@
         <v>210</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D211" s="4">
         <v>2.1214180759085677</v>
@@ -18134,10 +18137,10 @@
         <v>211</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D212" s="4">
         <v>1.3821044352272065</v>
@@ -18209,10 +18212,10 @@
         <v>212</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D213" s="4">
         <v>1.2902067087983424</v>
@@ -18284,10 +18287,10 @@
         <v>213</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D214" s="4">
         <v>1.4361476032224454</v>
@@ -18359,10 +18362,10 @@
         <v>214</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D215" s="4">
         <v>0.5746250124299828</v>
@@ -18434,10 +18437,10 @@
         <v>215</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D216" s="4">
         <v>0.5735369609352143</v>
@@ -18509,10 +18512,10 @@
         <v>216</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D217" s="4">
         <v>0.5710159814394324</v>
@@ -18584,10 +18587,10 @@
         <v>217</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D218" s="4">
         <v>0.5631847049473087</v>
@@ -18659,10 +18662,10 @@
         <v>218</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D219" s="4">
         <v>0.5631847049473087</v>
@@ -18734,10 +18737,10 @@
         <v>219</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D220" s="4">
         <v>0.5631847049473087</v>
@@ -18809,10 +18812,10 @@
         <v>220</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D221" s="4">
         <v>0.5631847049473087</v>
@@ -18884,10 +18887,10 @@
         <v>221</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D222" s="4">
         <v>0.5631847049473087</v>
@@ -18959,10 +18962,10 @@
         <v>222</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D223" s="4">
         <v>1.5921294770056387</v>
@@ -19034,10 +19037,10 @@
         <v>223</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D224" s="4">
         <v>1.8164598111400125</v>
@@ -19109,10 +19112,10 @@
         <v>224</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D225" s="4">
         <v>1.8164598111400125</v>
@@ -19184,10 +19187,10 @@
         <v>225</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D226" s="4">
         <v>1.8164598111400125</v>
@@ -19258,11 +19261,11 @@
         <f t="shared" si="1"/>
         <v>226</v>
       </c>
-      <c r="B227" s="3" t="s">
-        <v>337</v>
+      <c r="B227" s="7" t="s">
+        <v>338</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D227" s="4">
         <v>1.0349470270199594</v>
@@ -19297,8 +19300,8 @@
       <c r="N227" s="3">
         <v>0.0</v>
       </c>
-      <c r="O227" s="3" t="s">
-        <v>339</v>
+      <c r="O227" s="7" t="s">
+        <v>340</v>
       </c>
       <c r="P227" s="5"/>
       <c r="Q227" s="5"/>
@@ -19334,10 +19337,10 @@
         <v>227</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D228" s="4">
         <v>1.9311849547255207</v>
@@ -19409,10 +19412,10 @@
         <v>228</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D229" s="4">
         <v>0.9083622471351426</v>
@@ -19484,10 +19487,10 @@
         <v>229</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D230" s="4">
         <v>1.7174654948308699</v>
@@ -19559,10 +19562,10 @@
         <v>230</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D231" s="4">
         <v>2.7804617625220973</v>
@@ -19598,7 +19601,7 @@
         <v>0.0</v>
       </c>
       <c r="O231" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P231" s="5"/>
       <c r="Q231" s="5"/>
@@ -19634,10 +19637,10 @@
         <v>231</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D232" s="4">
         <v>2.60588913018932</v>
@@ -19673,7 +19676,7 @@
         <v>0.0</v>
       </c>
       <c r="O232" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P232" s="5"/>
       <c r="Q232" s="5"/>
@@ -19709,10 +19712,10 @@
         <v>232</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D233" s="4">
         <v>1.5261657561434896</v>
@@ -19784,10 +19787,10 @@
         <v>233</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D234" s="4">
         <v>1.548226055292188</v>
@@ -19859,10 +19862,10 @@
         <v>234</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D235" s="4">
         <v>1.626847334352457</v>
@@ -19934,10 +19937,10 @@
         <v>235</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D236" s="4">
         <v>1.8164598111400125</v>
@@ -20009,10 +20012,10 @@
         <v>236</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D237" s="4">
         <v>1.8164598111400125</v>
@@ -20084,10 +20087,10 @@
         <v>237</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D238" s="4">
         <v>1.8164598111400125</v>
@@ -20159,10 +20162,10 @@
         <v>238</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D239" s="4">
         <v>1.4062684033273385</v>
@@ -20234,10 +20237,10 @@
         <v>239</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D240" s="4">
         <v>1.4063294257249381</v>
@@ -20309,10 +20312,10 @@
         <v>240</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D241" s="4">
         <v>1.4064860682157465</v>
@@ -20384,10 +20387,10 @@
         <v>241</v>
       </c>
       <c r="B242" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C242" s="6" t="s">
         <v>368</v>
-      </c>
-      <c r="C242" s="6" t="s">
-        <v>367</v>
       </c>
       <c r="D242" s="4">
         <v>1.4064860682157465</v>
@@ -20459,10 +20462,10 @@
         <v>242</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D243" s="4">
         <v>1.4078849960408693</v>
@@ -20534,10 +20537,10 @@
         <v>243</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D244" s="4">
         <v>1.4081221202487315</v>
@@ -20609,10 +20612,10 @@
         <v>244</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D245" s="4">
         <v>1.4083772441970883</v>
@@ -20684,10 +20687,10 @@
         <v>245</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D246" s="4">
         <v>1.4471096567955477</v>
@@ -20759,10 +20762,10 @@
         <v>246</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D247" s="4">
         <v>1.2937365233808171</v>
@@ -20834,10 +20837,10 @@
         <v>247</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D248" s="4">
         <v>1.6357852375683588</v>
@@ -20909,10 +20912,10 @@
         <v>248</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D249" s="4">
         <v>1.2748198990847424</v>
@@ -20984,10 +20987,10 @@
         <v>249</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D250" s="4">
         <v>1.5681840203049555</v>
@@ -21059,10 +21062,10 @@
         <v>250</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D251" s="4">
         <v>1.5603486729753504</v>
@@ -21134,10 +21137,10 @@
         <v>251</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D252" s="4">
         <v>1.5495636726422397</v>
@@ -21209,10 +21212,10 @@
         <v>252</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D253" s="4">
         <v>1.5496119010656355</v>
@@ -21284,10 +21287,10 @@
         <v>253</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D254" s="4">
         <v>1.390076496360956</v>
@@ -21359,10 +21362,10 @@
         <v>254</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D255" s="4">
         <v>1.2786101831271355</v>
@@ -21434,10 +21437,10 @@
         <v>255</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D256" s="4">
         <v>1.5429713843498336</v>
@@ -21509,10 +21512,10 @@
         <v>256</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D257" s="4">
         <v>1.5360911323112711</v>
@@ -21584,10 +21587,10 @@
         <v>257</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D258" s="4">
         <v>1.5352740852130988</v>
@@ -21659,10 +21662,10 @@
         <v>258</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D259" s="4">
         <v>1.5368580386572002</v>
@@ -21734,10 +21737,10 @@
         <v>259</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D260" s="4">
         <v>1.7103200559679055</v>
@@ -21809,10 +21812,10 @@
         <v>260</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D261" s="4">
         <v>1.7103200559679055</v>
@@ -21884,10 +21887,10 @@
         <v>261</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D262" s="4">
         <v>1.7103200559679055</v>
@@ -21959,10 +21962,10 @@
         <v>262</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D263" s="4">
         <v>2.4405925148156027</v>
@@ -21998,7 +22001,7 @@
         <v>0.0</v>
       </c>
       <c r="O263" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P263" s="5"/>
       <c r="Q263" s="5"/>
@@ -22034,10 +22037,10 @@
         <v>263</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D264" s="4">
         <v>2.4405925148156027</v>
@@ -22073,7 +22076,7 @@
         <v>0.0</v>
       </c>
       <c r="O264" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P264" s="5"/>
       <c r="Q264" s="5"/>
@@ -22109,10 +22112,10 @@
         <v>264</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D265" s="4">
         <v>1.6303192076656852</v>
@@ -22184,10 +22187,10 @@
         <v>265</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D266" s="4">
         <v>1.350032109573688</v>
@@ -22259,10 +22262,10 @@
         <v>266</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D267" s="4">
         <v>0.9625421824471605</v>
@@ -22334,10 +22337,10 @@
         <v>267</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D268" s="4">
         <v>1.672016395646727</v>
@@ -22409,10 +22412,10 @@
         <v>268</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D269" s="4">
         <v>1.6857708833245104</v>
@@ -22484,10 +22487,10 @@
         <v>269</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D270" s="4">
         <v>1.4906443932632514</v>
@@ -22559,10 +22562,10 @@
         <v>270</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D271" s="4">
         <v>1.4906443932632514</v>
@@ -22634,10 +22637,10 @@
         <v>271</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D272" s="4">
         <v>2.170757959781809</v>
@@ -22673,7 +22676,7 @@
         <v>0.0</v>
       </c>
       <c r="O272" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P272" s="5"/>
       <c r="Q272" s="5"/>
@@ -22709,10 +22712,10 @@
         <v>272</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D273" s="4">
         <v>1.4901122539591773</v>
@@ -22784,10 +22787,10 @@
         <v>273</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D274" s="4">
         <v>1.3682764263609946</v>
@@ -22859,10 +22862,10 @@
         <v>274</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D275" s="4">
         <v>1.6170395520943595</v>
@@ -22934,10 +22937,10 @@
         <v>275</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D276" s="4">
         <v>1.5873169401468161</v>
@@ -23009,10 +23012,10 @@
         <v>276</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D277" s="4">
         <v>2.268995876353111</v>
@@ -23048,7 +23051,7 @@
         <v>0.0</v>
       </c>
       <c r="O277" s="8" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P277" s="5"/>
       <c r="Q277" s="5"/>
@@ -23084,10 +23087,10 @@
         <v>277</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D278" s="4">
         <v>1.5377759354439549</v>
@@ -23159,10 +23162,10 @@
         <v>278</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D279" s="4">
         <v>2.060833310351088</v>
@@ -23234,10 +23237,10 @@
         <v>279</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D280" s="4">
         <v>1.64137609</v>
@@ -23309,10 +23312,10 @@
         <v>280</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D281" s="4">
         <v>1.64137609</v>
@@ -23384,10 +23387,10 @@
         <v>281</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D282" s="4">
         <v>1.64137609</v>
@@ -23459,10 +23462,10 @@
         <v>282</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D283" s="4">
         <v>1.64137609</v>
@@ -23534,10 +23537,10 @@
         <v>283</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D284" s="4">
         <v>1.64137609</v>
@@ -23609,10 +23612,10 @@
         <v>284</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D285" s="4">
         <v>3.062163</v>
@@ -23648,7 +23651,7 @@
         <v>1.0</v>
       </c>
       <c r="O285" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P285" s="5"/>
       <c r="Q285" s="5"/>
@@ -23684,10 +23687,10 @@
         <v>285</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D286" s="4">
         <v>1.6164165982598042</v>
@@ -23759,10 +23762,10 @@
         <v>286</v>
       </c>
       <c r="B287" s="7" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C287" s="7" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D287" s="4">
         <v>2.435928152594442</v>
@@ -23798,7 +23801,7 @@
         <v>0.0</v>
       </c>
       <c r="O287" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P287" s="5"/>
       <c r="Q287" s="5"/>
@@ -23834,10 +23837,10 @@
         <v>287</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D288" s="4">
         <v>2.5662335881863716</v>
@@ -23909,10 +23912,10 @@
         <v>288</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D289" s="4">
         <v>2.5662335881863716</v>
@@ -23984,10 +23987,10 @@
         <v>289</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D290" s="4">
         <v>1.7130154745011708</v>
@@ -24059,10 +24062,10 @@
         <v>290</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D291" s="4">
         <v>1.7130154745011708</v>
@@ -24134,10 +24137,10 @@
         <v>291</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D292" s="4">
         <v>0.8687339510852222</v>
@@ -24209,10 +24212,10 @@
         <v>292</v>
       </c>
       <c r="B293" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D293" s="4">
         <v>1.490745579683119</v>
@@ -24284,10 +24287,10 @@
         <v>293</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D294" s="4">
         <v>1.390666318139661</v>
@@ -24359,10 +24362,10 @@
         <v>294</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D295" s="4">
         <v>1.390666318139661</v>
@@ -24434,10 +24437,10 @@
         <v>295</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D296" s="4">
         <v>1.390666318139661</v>
@@ -24509,10 +24512,10 @@
         <v>296</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D297" s="4">
         <v>2.2604180390838278</v>
@@ -24584,10 +24587,10 @@
         <v>297</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D298" s="4">
         <v>2.2604180390838278</v>
@@ -24659,10 +24662,10 @@
         <v>298</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D299" s="4">
         <v>2.2604180390838278</v>
@@ -24734,10 +24737,10 @@
         <v>299</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D300" s="4">
         <v>0.5830666945929888</v>
@@ -24809,10 +24812,10 @@
         <v>300</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D301" s="4">
         <v>0.5830666945929888</v>
@@ -24884,10 +24887,10 @@
         <v>301</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D302" s="4">
         <v>0.5830666945929888</v>
@@ -24959,10 +24962,10 @@
         <v>302</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D303" s="4">
         <v>0.5830666945929888</v>
@@ -25034,10 +25037,10 @@
         <v>303</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D304" s="4">
         <v>0.5830666945929888</v>
@@ -25109,10 +25112,10 @@
         <v>304</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C305" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D305" s="4">
         <v>0.5830666945929888</v>
@@ -25184,10 +25187,10 @@
         <v>305</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D306" s="4">
         <v>0.5830666945929888</v>
@@ -25259,10 +25262,10 @@
         <v>306</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D307" s="4">
         <v>0.5830666945929888</v>
@@ -25334,10 +25337,10 @@
         <v>307</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D308" s="4">
         <v>0.5830666945929888</v>
@@ -25409,10 +25412,10 @@
         <v>308</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D309" s="4">
         <v>1.6020421254875896</v>
@@ -25484,10 +25487,10 @@
         <v>309</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C310" s="10" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D310" s="4">
         <v>0.8886951480024474</v>
@@ -25523,7 +25526,7 @@
         <v>0.0</v>
       </c>
       <c r="O310" s="7" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P310" s="5"/>
       <c r="Q310" s="5"/>
@@ -25559,10 +25562,10 @@
         <v>310</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D311" s="4">
         <v>0.5680490223650436</v>
@@ -25634,10 +25637,10 @@
         <v>311</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D312" s="4">
         <v>0.5680490223650436</v>
@@ -25709,10 +25712,10 @@
         <v>312</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D313" s="4">
         <v>0.49513442517672046</v>
@@ -25784,10 +25787,10 @@
         <v>313</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D314" s="4">
         <v>0.49513442517672046</v>
@@ -25859,7 +25862,7 @@
         <v>314</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C315" s="3">
         <v>1955.0</v>
@@ -25934,10 +25937,10 @@
         <v>315</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D316" s="4">
         <v>1.6615680543409397</v>
@@ -26009,10 +26012,10 @@
         <v>316</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D317" s="4">
         <v>1.6615680543409397</v>
@@ -26084,10 +26087,10 @@
         <v>317</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D318" s="4">
         <v>1.6615680543409397</v>
@@ -26159,10 +26162,10 @@
         <v>318</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D319" s="4">
         <v>1.6615680543409397</v>
@@ -26234,10 +26237,10 @@
         <v>319</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D320" s="4">
         <v>1.6615680543409397</v>
@@ -26309,10 +26312,10 @@
         <v>320</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D321" s="4">
         <v>0.5690307155432264</v>
@@ -26384,10 +26387,10 @@
         <v>321</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D322" s="4">
         <v>0.5690307155432264</v>
@@ -26459,10 +26462,10 @@
         <v>322</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D323" s="4">
         <v>0.5690307155432264</v>
@@ -26534,10 +26537,10 @@
         <v>323</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D324" s="4">
         <v>0.5690307155432264</v>
@@ -26609,10 +26612,10 @@
         <v>324</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D325" s="4">
         <v>0.5690307155432264</v>
@@ -26684,10 +26687,10 @@
         <v>325</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D326" s="4">
         <v>0.5690307155432264</v>
@@ -26759,10 +26762,10 @@
         <v>326</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D327" s="4">
         <v>0.5690307155432264</v>
@@ -26834,10 +26837,10 @@
         <v>327</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D328" s="4">
         <v>0.5690307155432264</v>
@@ -26909,10 +26912,10 @@
         <v>328</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D329" s="4">
         <v>0.5690307155432264</v>
@@ -26984,10 +26987,10 @@
         <v>329</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D330" s="4">
         <v>0.5690307155432264</v>
@@ -27059,10 +27062,10 @@
         <v>330</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D331" s="4">
         <v>0.5690307155432264</v>
@@ -27134,10 +27137,10 @@
         <v>331</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D332" s="4">
         <v>0.5690307155432264</v>
@@ -27209,10 +27212,10 @@
         <v>332</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D333" s="4">
         <v>0.5690307155432264</v>
@@ -27284,10 +27287,10 @@
         <v>333</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D334" s="4">
         <v>0.5690307155432264</v>
@@ -27359,10 +27362,10 @@
         <v>334</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C335" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D335" s="4">
         <v>0.5690307155432264</v>
@@ -27434,10 +27437,10 @@
         <v>335</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D336" s="4">
         <v>0.5690307155432264</v>
@@ -27509,10 +27512,10 @@
         <v>336</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D337" s="4">
         <v>0.5690307155432264</v>
@@ -27584,10 +27587,10 @@
         <v>337</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D338" s="4">
         <v>0.5690307155432264</v>
@@ -27659,10 +27662,10 @@
         <v>338</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D339" s="4">
         <v>1.739947109709108</v>
@@ -27734,10 +27737,10 @@
         <v>339</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D340" s="4">
         <v>1.739947109709108</v>
@@ -27809,10 +27812,10 @@
         <v>340</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D341" s="4">
         <v>1.739947109709108</v>
@@ -27884,10 +27887,10 @@
         <v>341</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D342" s="4">
         <v>1.739947109709108</v>
@@ -27959,10 +27962,10 @@
         <v>342</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D343" s="4">
         <v>1.739947109709108</v>
@@ -28034,10 +28037,10 @@
         <v>343</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D344" s="4">
         <v>1.739947109709108</v>
@@ -28109,10 +28112,10 @@
         <v>344</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D345" s="4">
         <v>1.739947109709108</v>
@@ -28184,10 +28187,10 @@
         <v>345</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D346" s="4">
         <v>2.0001516349770174</v>
@@ -28223,7 +28226,7 @@
         <v>0.0</v>
       </c>
       <c r="O346" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P346" s="5"/>
       <c r="Q346" s="5"/>
@@ -28259,10 +28262,10 @@
         <v>346</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D347" s="4">
         <v>2.0001516349770174</v>
@@ -28298,7 +28301,7 @@
         <v>0.0</v>
       </c>
       <c r="O347" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P347" s="5"/>
       <c r="Q347" s="5"/>
@@ -28334,10 +28337,10 @@
         <v>347</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D348" s="4">
         <v>2.0001516349770174</v>
@@ -28373,7 +28376,7 @@
         <v>0.0</v>
       </c>
       <c r="O348" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P348" s="5"/>
       <c r="Q348" s="5"/>
@@ -28409,10 +28412,10 @@
         <v>348</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D349" s="4">
         <v>1.9988469539468372</v>
@@ -28484,10 +28487,10 @@
         <v>349</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C350" s="6" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D350" s="4">
         <v>1.161628</v>
@@ -28523,7 +28526,7 @@
         <v>0.0</v>
       </c>
       <c r="O350" s="7" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P350" s="5"/>
       <c r="Q350" s="5"/>
@@ -28559,10 +28562,10 @@
         <v>350</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D351" s="4">
         <v>0.555487056091735</v>
@@ -28634,10 +28637,10 @@
         <v>351</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D352" s="4">
         <v>0.555487056091735</v>
@@ -28709,10 +28712,10 @@
         <v>352</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D353" s="4">
         <v>0.555487056091735</v>
@@ -28784,10 +28787,10 @@
         <v>353</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D354" s="4">
         <v>0.555487056091735</v>
@@ -28859,10 +28862,10 @@
         <v>354</v>
       </c>
       <c r="B355" s="6" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C355" s="6" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D355" s="4">
         <v>1.3285392523061559</v>
@@ -28934,10 +28937,10 @@
         <v>355</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D356" s="4">
         <v>1.585011359384095</v>
@@ -29009,10 +29012,10 @@
         <v>356</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D357" s="4">
         <v>1.585011359384095</v>
@@ -29084,10 +29087,10 @@
         <v>357</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C358" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D358" s="4">
         <v>1.627580492289293</v>
@@ -29159,10 +29162,10 @@
         <v>358</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C359" s="6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D359" s="4">
         <v>1.877494693955877</v>
@@ -29234,10 +29237,10 @@
         <v>359</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C360" s="6" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D360" s="4">
         <v>1.877494693955877</v>
@@ -29309,10 +29312,10 @@
         <v>360</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C361" s="6" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D361" s="4">
         <v>1.877494693955877</v>
@@ -29384,10 +29387,10 @@
         <v>361</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D362" s="4">
         <v>2.413448073613454</v>
@@ -29423,7 +29426,7 @@
         <v>0.0</v>
       </c>
       <c r="O362" s="7" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P362" s="5"/>
       <c r="Q362" s="5"/>
@@ -29459,10 +29462,10 @@
         <v>362</v>
       </c>
       <c r="B363" s="6" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C363" s="6" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D363" s="4">
         <v>1.8611463420194052</v>
@@ -29534,7 +29537,7 @@
         <v>363</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C364" s="6">
         <v>1.0</v>
@@ -29573,7 +29576,7 @@
         <v>0.0</v>
       </c>
       <c r="O364" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P364" s="5"/>
       <c r="Q364" s="5"/>
@@ -29609,7 +29612,7 @@
         <v>364</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C365" s="6">
         <v>2.0</v>
@@ -29648,7 +29651,7 @@
         <v>0.0</v>
       </c>
       <c r="O365" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P365" s="5"/>
       <c r="Q365" s="5"/>
@@ -29684,7 +29687,7 @@
         <v>365</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C366" s="6">
         <v>3.0</v>
@@ -29723,7 +29726,7 @@
         <v>0.0</v>
       </c>
       <c r="O366" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P366" s="5"/>
       <c r="Q366" s="5"/>
@@ -29759,7 +29762,7 @@
         <v>366</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C367" s="3">
         <v>5.0</v>
@@ -29834,7 +29837,7 @@
         <v>367</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C368" s="3">
         <v>6.0</v>
@@ -29909,7 +29912,7 @@
         <v>368</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C369" s="3">
         <v>7.0</v>
@@ -29984,7 +29987,7 @@
         <v>369</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C370" s="3">
         <v>8.0</v>
@@ -30059,10 +30062,10 @@
         <v>370</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C371" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D371" s="4">
         <v>0.5735601678523796</v>
@@ -30098,7 +30101,7 @@
         <v>0.0</v>
       </c>
       <c r="O371" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="P371" s="5"/>
       <c r="Q371" s="5"/>
@@ -30134,10 +30137,10 @@
         <v>371</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D372" s="4">
         <v>0.5735601678523796</v>
@@ -30209,10 +30212,10 @@
         <v>372</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D373" s="4">
         <v>1.716733680653522</v>
@@ -30284,10 +30287,10 @@
         <v>373</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C374" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D374" s="4">
         <v>1.7407652343457507</v>
@@ -30359,10 +30362,10 @@
         <v>374</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C375" s="6" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D375" s="4">
         <v>2.8146485891203645</v>
@@ -30434,10 +30437,10 @@
         <v>375</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C376" s="6" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D376" s="4">
         <v>2.8146485891203645</v>
@@ -30473,7 +30476,7 @@
         <v>0.0</v>
       </c>
       <c r="O376" s="7" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="P376" s="5"/>
       <c r="Q376" s="5"/>
@@ -30509,10 +30512,10 @@
         <v>376</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D377" s="4">
         <v>2.8146485891203645</v>
@@ -30548,7 +30551,7 @@
         <v>0.0</v>
       </c>
       <c r="O377" s="7" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="P377" s="5"/>
       <c r="Q377" s="5"/>
@@ -30584,10 +30587,10 @@
         <v>377</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D378" s="4">
         <v>2.8146485891203645</v>
@@ -30623,7 +30626,7 @@
         <v>0.0</v>
       </c>
       <c r="O378" s="7" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="P378" s="5"/>
       <c r="Q378" s="5"/>
@@ -30659,10 +30662,10 @@
         <v>378</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C379" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D379" s="4">
         <v>2.8146485891203645</v>
@@ -30698,7 +30701,7 @@
         <v>0.0</v>
       </c>
       <c r="O379" s="7" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="P379" s="5"/>
       <c r="Q379" s="5"/>
@@ -30734,10 +30737,10 @@
         <v>379</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C380" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D380" s="4">
         <v>2.8146485891203645</v>
@@ -30773,7 +30776,7 @@
         <v>0.0</v>
       </c>
       <c r="O380" s="7" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="P380" s="5"/>
       <c r="Q380" s="5"/>
@@ -30809,10 +30812,10 @@
         <v>380</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D381" s="4">
         <v>2.8146485891203645</v>
@@ -30848,7 +30851,7 @@
         <v>0.0</v>
       </c>
       <c r="O381" s="7" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="P381" s="5"/>
       <c r="Q381" s="5"/>
@@ -30884,10 +30887,10 @@
         <v>381</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D382" s="4">
         <v>2.8146485891203645</v>
@@ -30923,7 +30926,7 @@
         <v>0.0</v>
       </c>
       <c r="O382" s="7" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="P382" s="5"/>
       <c r="Q382" s="5"/>
@@ -30959,10 +30962,10 @@
         <v>382</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C383" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D383" s="4">
         <v>2.8146485891203645</v>
@@ -30998,7 +31001,7 @@
         <v>0.0</v>
       </c>
       <c r="O383" s="7" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="P383" s="5"/>
       <c r="Q383" s="5"/>
@@ -31034,10 +31037,10 @@
         <v>383</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D384" s="4">
         <v>2.8146485891203645</v>
@@ -31073,7 +31076,7 @@
         <v>0.0</v>
       </c>
       <c r="O384" s="7" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="P384" s="5"/>
       <c r="Q384" s="5"/>
@@ -31109,10 +31112,10 @@
         <v>384</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D385" s="4">
         <v>2.8146485891203645</v>
@@ -31148,7 +31151,7 @@
         <v>0.0</v>
       </c>
       <c r="O385" s="7" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="P385" s="5"/>
       <c r="Q385" s="5"/>
@@ -31184,10 +31187,10 @@
         <v>385</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D386" s="4">
         <v>1.251051022480634</v>
@@ -31259,10 +31262,10 @@
         <v>386</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D387" s="4">
         <v>1.6970351996066801</v>
@@ -31334,10 +31337,10 @@
         <v>387</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D388" s="4">
         <v>1.6970351996066801</v>
@@ -31373,7 +31376,7 @@
         <v>0.0</v>
       </c>
       <c r="O388" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P388" s="5"/>
       <c r="Q388" s="5"/>
@@ -31409,10 +31412,10 @@
         <v>388</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D389" s="4">
         <v>2.1670159467527923</v>
@@ -31448,7 +31451,7 @@
         <v>0.0</v>
       </c>
       <c r="O389" s="7" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P389" s="5"/>
       <c r="Q389" s="5"/>
@@ -31484,10 +31487,10 @@
         <v>389</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C390" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D390" s="4">
         <v>1.9713819752876685</v>
@@ -31559,10 +31562,10 @@
         <v>390</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C391" s="3" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D391" s="4">
         <v>2.3586239427025912</v>
@@ -31634,10 +31637,10 @@
         <v>391</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C392" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D392" s="4">
         <v>2.3586239427025912</v>
@@ -31709,10 +31712,10 @@
         <v>392</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C393" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D393" s="4">
         <v>2.0546339961474076</v>
@@ -31784,10 +31787,10 @@
         <v>393</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D394" s="4">
         <v>2.060470049677191</v>
@@ -31859,10 +31862,10 @@
         <v>394</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C395" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D395" s="4">
         <v>2.8383154069800414</v>
@@ -31898,7 +31901,7 @@
         <v>0.0</v>
       </c>
       <c r="O395" s="7" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="P395" s="5"/>
       <c r="Q395" s="5"/>
@@ -31934,10 +31937,10 @@
         <v>395</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C396" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D396" s="4">
         <v>2.8383154069800414</v>
@@ -31973,7 +31976,7 @@
         <v>0.0</v>
       </c>
       <c r="O396" s="7" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="P396" s="5"/>
       <c r="Q396" s="5"/>
@@ -32009,10 +32012,10 @@
         <v>396</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C397" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D397" s="4">
         <v>2.8383154069800414</v>
@@ -32048,7 +32051,7 @@
         <v>0.0</v>
       </c>
       <c r="O397" s="7" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="P397" s="5"/>
       <c r="Q397" s="5"/>
@@ -32084,10 +32087,10 @@
         <v>397</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C398" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D398" s="4">
         <v>2.8383154069800414</v>
@@ -32123,7 +32126,7 @@
         <v>0.0</v>
       </c>
       <c r="O398" s="7" t="s">
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="P398" s="5"/>
       <c r="Q398" s="5"/>
@@ -32159,10 +32162,10 @@
         <v>398</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C399" s="6" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D399" s="4">
         <v>1.4899580501913723</v>
@@ -32234,10 +32237,10 @@
         <v>399</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C400" s="6" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D400" s="4">
         <v>1.5841673623156716</v>
@@ -32309,10 +32312,10 @@
         <v>400</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C401" s="6" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D401" s="4">
         <v>1.6183191590861141</v>
@@ -32384,10 +32387,10 @@
         <v>401</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C402" s="6" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D402" s="4">
         <v>1.6110482379320648</v>
@@ -32459,10 +32462,10 @@
         <v>402</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C403" s="3" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D403" s="4">
         <v>1.5211250390421183</v>
@@ -32534,10 +32537,10 @@
         <v>403</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C404" s="6" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D404" s="4">
         <v>1.5854985019097934</v>
@@ -32609,10 +32612,10 @@
         <v>404</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C405" s="6" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D405" s="4">
         <v>1.585462908886692</v>
@@ -32684,10 +32687,10 @@
         <v>405</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C406" s="6" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D406" s="4">
         <v>1.314459392957068</v>
@@ -32759,10 +32762,10 @@
         <v>406</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C407" s="3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D407" s="4">
         <v>1.7103420327276286</v>
@@ -32834,10 +32837,10 @@
         <v>407</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C408" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D408" s="4">
         <v>2.014227552466607</v>
@@ -32909,10 +32912,10 @@
         <v>408</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C409" s="3" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D409" s="4">
         <v>2.9494324023290446</v>
@@ -32984,10 +32987,10 @@
         <v>409</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C410" s="3" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D410" s="4">
         <v>1.7430049318041911</v>
@@ -33023,7 +33026,7 @@
         <v>0.0</v>
       </c>
       <c r="O410" s="3" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="P410" s="5"/>
       <c r="Q410" s="5"/>
@@ -33059,10 +33062,10 @@
         <v>410</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C411" s="3" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D411" s="4">
         <v>0.5631847049473087</v>
@@ -33134,10 +33137,10 @@
         <v>411</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C412" s="3" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D412" s="4">
         <v>1.5824342612689055</v>
@@ -33209,10 +33212,10 @@
         <v>412</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C413" s="6" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D413" s="4">
         <v>1.377198863168076</v>
@@ -33284,10 +33287,10 @@
         <v>413</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C414" s="3" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D414" s="4">
         <v>1.7228500259602229</v>
@@ -33359,10 +33362,10 @@
         <v>414</v>
       </c>
       <c r="B415" s="6" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C415" s="6" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D415" s="4">
         <v>1.6754570833095375</v>
@@ -33434,10 +33437,10 @@
         <v>415</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C416" s="6" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D416" s="4">
         <v>1.6537938332913538</v>
@@ -33509,10 +33512,10 @@
         <v>416</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C417" s="6" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D417" s="4">
         <v>1.6537938332913538</v>
@@ -33584,10 +33587,10 @@
         <v>417</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C418" s="3" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D418" s="4">
         <v>1.6855486960731034</v>
@@ -33659,10 +33662,10 @@
         <v>418</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C419" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D419" s="4">
         <v>1.532095581710081</v>
@@ -33734,10 +33737,10 @@
         <v>419</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C420" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D420" s="4">
         <v>1.532095581710081</v>
@@ -33809,10 +33812,10 @@
         <v>420</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C421" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D421" s="4">
         <v>1.532095581710081</v>
@@ -33884,10 +33887,10 @@
         <v>421</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C422" s="3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D422" s="4">
         <v>1.532156954732725</v>
@@ -33959,10 +33962,10 @@
         <v>422</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C423" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D423" s="4">
         <v>1.7225229192304183</v>
@@ -34034,10 +34037,10 @@
         <v>423</v>
       </c>
       <c r="B424" s="6" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C424" s="6" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D424" s="4">
         <v>1.2524227214108592</v>
